--- a/data/trans_dic/IP19C08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor</t>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,95</t>
+          <t>0,0; 52,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,73</t>
+          <t>0,0; 28,28</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 14,33</t>
+          <t>4,42; 14,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,9</t>
+          <t>2,42; 11,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 11,75</t>
+          <t>2,42; 12,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,75</t>
+          <t>0,99; 8,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 13,51</t>
+          <t>3,38; 13,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,76</t>
+          <t>2,32; 10,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,99</t>
+          <t>0,74; 7,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,77</t>
+          <t>4,53; 11,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,87</t>
+          <t>2,97; 8,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,34</t>
+          <t>1,55; 6,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,82</t>
+          <t>1,22; 5,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 13,08</t>
+          <t>4,19; 13,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,31</t>
+          <t>3,41; 10,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,77</t>
+          <t>1,63; 6,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,74</t>
+          <t>1,06; 6,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 11,48</t>
+          <t>3,29; 11,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,26</t>
+          <t>1,58; 7,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 7,43</t>
+          <t>1,88; 7,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,32</t>
+          <t>1,6; 6,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,55</t>
+          <t>4,67; 10,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,73</t>
+          <t>3,03; 7,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,09</t>
+          <t>2,38; 5,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,56</t>
+          <t>1,87; 5,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,86</t>
+          <t>1,52; 5,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,7</t>
+          <t>0,46; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,53</t>
+          <t>1,26; 6,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,64</t>
+          <t>0,29; 2,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,53</t>
+          <t>1,36; 5,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,96</t>
+          <t>0,99; 5,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,76</t>
+          <t>0,53; 4,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,83</t>
+          <t>1,09; 10,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,67</t>
+          <t>1,85; 4,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,12</t>
+          <t>1,16; 4,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,63</t>
+          <t>1,16; 4,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,04</t>
+          <t>0,98; 6,26</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,89</t>
+          <t>3,97; 8,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,28</t>
+          <t>2,81; 6,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,76</t>
+          <t>2,39; 5,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,83</t>
+          <t>1,16; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,93</t>
+          <t>3,29; 6,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,51</t>
+          <t>2,42; 5,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,47</t>
+          <t>1,44; 4,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,51</t>
+          <t>1,87; 6,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,79</t>
+          <t>4,06; 7,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,25</t>
+          <t>2,84; 5,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,37</t>
+          <t>2,28; 4,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,61</t>
+          <t>1,88; 4,56</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por selladores, aplicación de flúor (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3046</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3143</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7070</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4406</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1863</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12623</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4054</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3725; 12468</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1882; 8816</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1648; 8253</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657; 5887</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2720; 10461</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2138; 9519</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4038</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>573; 5512</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7457; 18807</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5044; 14747</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2324; 10000</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1745; 8066</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7765</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7763</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5428</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3741</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6914</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6137</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14679</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12684</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9676</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4156; 13101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4270; 13713</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2429; 9753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1298; 8124</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3474; 12073</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2082; 9919</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2805; 10974</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2636; 10978</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9571; 22046</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7794; 19252</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7099; 17832</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5358; 16283</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4068</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8571</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6846</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10511</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2489; 9771</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>675; 6280</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1826; 9251</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>565; 5342</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2361; 9222</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1401; 8165</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>715; 6206</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2587; 24497</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6233; 15715</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3360; 12259</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3244; 13659</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4252; 27242</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14912</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13833</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>37508</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28703</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>23546</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>25037</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13941; 28110</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9961; 22226</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8671; 21266</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4549; 13992</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11913; 25213</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8871; 20132</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5302; 15297</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9080; 32013</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>28943; 50166</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20456; 37950</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16612; 31921</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16461; 39989</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Edad-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,54</t>
+          <t>0,0; 58,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,28</t>
+          <t>0,0; 33,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 14,78</t>
+          <t>4,21; 14,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 11,35</t>
+          <t>1,98; 11,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 12,13</t>
+          <t>2,34; 11,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,89</t>
+          <t>0,86; 9,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 13,01</t>
+          <t>3,26; 12,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,34</t>
+          <t>2,16; 10,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,15</t>
+          <t>0,73; 6,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 11,42</t>
+          <t>4,74; 11,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,69</t>
+          <t>2,94; 9,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,66</t>
+          <t>1,41; 6,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,63</t>
+          <t>1,22; 5,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 13,21</t>
+          <t>3,94; 13,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 10,96</t>
+          <t>3,28; 10,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,55</t>
+          <t>1,72; 7,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,66</t>
+          <t>1,07; 6,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 11,42</t>
+          <t>3,21; 11,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,51</t>
+          <t>1,6; 7,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,35</t>
+          <t>2,17; 7,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,66</t>
+          <t>1,72; 7,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,76</t>
+          <t>4,55; 10,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,49</t>
+          <t>2,96; 7,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,98</t>
+          <t>2,37; 6,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,68</t>
+          <t>1,84; 5,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,98</t>
+          <t>1,5; 5,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,25</t>
+          <t>0,46; 4,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,38</t>
+          <t>1,22; 6,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,7</t>
+          <t>0,28; 2,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,31</t>
+          <t>1,39; 5,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,78</t>
+          <t>1,01; 5,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,62</t>
+          <t>0,54; 4,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,33</t>
+          <t>1,09; 10,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,66</t>
+          <t>1,85; 4,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,24</t>
+          <t>1,18; 4,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,89</t>
+          <t>1,21; 4,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,26</t>
+          <t>0,96; 6,1</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,01</t>
+          <t>3,98; 7,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,28</t>
+          <t>2,58; 6,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,86</t>
+          <t>2,38; 5,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,57</t>
+          <t>1,24; 3,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,97</t>
+          <t>3,13; 6,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,5</t>
+          <t>2,25; 5,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,17</t>
+          <t>1,44; 4,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,61</t>
+          <t>1,96; 6,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,04</t>
+          <t>4,03; 6,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,27</t>
+          <t>2,85; 5,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,37</t>
+          <t>2,24; 4,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,56</t>
+          <t>1,86; 4,54</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3046</t>
+          <t>0; 3398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3143</t>
+          <t>0; 3737</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3725; 12468</t>
+          <t>3553; 12294</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1882; 8816</t>
+          <t>1539; 9302</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1648; 8253</t>
+          <t>1593; 7847</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>657; 5887</t>
+          <t>570; 6177</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2720; 10461</t>
+          <t>2624; 10082</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2138; 9519</t>
+          <t>1987; 9337</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4038</t>
+          <t>0; 4933</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>573; 5512</t>
+          <t>563; 5210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7457; 18807</t>
+          <t>7814; 19244</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5044; 14747</t>
+          <t>4997; 15843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2324; 10000</t>
+          <t>2112; 9618</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1745; 8066</t>
+          <t>1755; 8422</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4156; 13101</t>
+          <t>3906; 13389</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4270; 13713</t>
+          <t>4106; 13736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2429; 9753</t>
+          <t>2556; 10824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1298; 8124</t>
+          <t>1310; 8363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3474; 12073</t>
+          <t>3398; 11968</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2082; 9919</t>
+          <t>2111; 9709</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2805; 10974</t>
+          <t>3234; 11045</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2636; 10978</t>
+          <t>2834; 12422</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9571; 22046</t>
+          <t>9332; 21378</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7794; 19252</t>
+          <t>7600; 19102</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7099; 17832</t>
+          <t>7062; 18190</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5358; 16283</t>
+          <t>5270; 16410</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2489; 9771</t>
+          <t>2445; 9142</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>675; 6280</t>
+          <t>681; 7059</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1826; 9251</t>
+          <t>1768; 9993</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>565; 5342</t>
+          <t>556; 5185</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2361; 9222</t>
+          <t>2411; 9666</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1401; 8165</t>
+          <t>1426; 8346</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>715; 6206</t>
+          <t>720; 6362</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2587; 24497</t>
+          <t>2584; 24808</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6233; 15715</t>
+          <t>6225; 15984</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3360; 12259</t>
+          <t>3401; 12192</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3244; 13659</t>
+          <t>3389; 12701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4252; 27242</t>
+          <t>4173; 26536</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13941; 28110</t>
+          <t>13968; 27982</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9961; 22226</t>
+          <t>9148; 21767</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8671; 21266</t>
+          <t>8625; 21034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4549; 13992</t>
+          <t>4838; 14905</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11913; 25213</t>
+          <t>11336; 24622</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8871; 20132</t>
+          <t>8242; 20937</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5302; 15297</t>
+          <t>5292; 15409</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9080; 32013</t>
+          <t>9516; 32833</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28943; 50166</t>
+          <t>28707; 48048</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20456; 37950</t>
+          <t>20538; 38228</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16612; 31921</t>
+          <t>16379; 31571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16461; 39989</t>
+          <t>16252; 39753</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C08-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,27 +684,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 51,62</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,63</t>
+          <t>0,0; 28,54</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,58</t>
+          <t>3,32; 13,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,97</t>
+          <t>2,18; 9,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,53</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,33</t>
+          <t>0,63; 6,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,54</t>
+          <t>4,16; 14,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,14</t>
+          <t>2,51; 11,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>2,35; 11,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,75</t>
+          <t>0,97; 8,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,68</t>
+          <t>4,83; 11,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,33</t>
+          <t>3,01; 8,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,4</t>
+          <t>1,54; 6,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,88</t>
+          <t>1,29; 5,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 13,5</t>
+          <t>3,44; 11,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 10,98</t>
+          <t>1,57; 7,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,27</t>
+          <t>1,8; 7,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,86</t>
+          <t>1,66; 7,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,32</t>
+          <t>4,2; 13,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,35</t>
+          <t>3,35; 10,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,4</t>
+          <t>1,64; 6,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,54</t>
+          <t>0,97; 6,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,43</t>
+          <t>4,65; 10,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,43</t>
+          <t>2,96; 7,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,1</t>
+          <t>2,36; 6,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,72</t>
+          <t>1,7; 5,55</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,11%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,59</t>
+          <t>1,35; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,77</t>
+          <t>1,0; 5,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,89</t>
+          <t>0,53; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,62</t>
+          <t>0,84; 11,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,56</t>
+          <t>1,23; 5,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,91</t>
+          <t>0,46; 4,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,73</t>
+          <t>1,35; 6,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,46</t>
+          <t>0,28; 2,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,74</t>
+          <t>1,8; 4,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,22</t>
+          <t>1,18; 4,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,54</t>
+          <t>1,21; 4,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,1</t>
+          <t>0,97; 6,04</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,97</t>
+          <t>3,21; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,15</t>
+          <t>2,39; 5,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,8</t>
+          <t>1,57; 4,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,81</t>
+          <t>1,81; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,81</t>
+          <t>4,08; 7,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,72</t>
+          <t>2,54; 6,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,2</t>
+          <t>2,39; 5,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,78</t>
+          <t>1,12; 3,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,74</t>
+          <t>4,05; 6,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,31</t>
+          <t>2,9; 5,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,33</t>
+          <t>2,19; 4,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,54</t>
+          <t>1,92; 4,7</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,27 +1612,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>808</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3398</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1680,27 +1680,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0; 3134</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3737</t>
+          <t>0; 3068</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7070</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4406</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3887</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5553</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>3574</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3553; 12294</t>
+          <t>2671; 10862</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1539; 9302</t>
+          <t>2010; 8987</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1593; 7847</t>
+          <t>0; 3956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>570; 6177</t>
+          <t>427; 4434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2624; 10082</t>
+          <t>3509; 12082</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1987; 9337</t>
+          <t>1950; 9245</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4933</t>
+          <t>1602; 7998</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>563; 5210</t>
+          <t>617; 5637</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7814; 19244</t>
+          <t>7964; 19396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4997; 15843</t>
+          <t>5112; 15057</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2112; 9618</t>
+          <t>2316; 9526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1755; 8422</t>
+          <t>1690; 7663</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6914</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6137</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7765</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7763</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5428</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3741</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6914</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6137</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9369</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3906; 13389</t>
+          <t>3639; 12132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4106; 13736</t>
+          <t>2073; 9584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2556; 10824</t>
+          <t>2691; 11101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1310; 8363</t>
+          <t>2584; 11585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3398; 11968</t>
+          <t>4169; 12975</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2111; 9709</t>
+          <t>4192; 12893</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3234; 11045</t>
+          <t>2445; 10089</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2834; 12422</t>
+          <t>1185; 8503</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9332; 21378</t>
+          <t>9519; 21615</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7600; 19102</t>
+          <t>7615; 19886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7062; 18190</t>
+          <t>7033; 18175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5270; 16410</t>
+          <t>4721; 15387</t>
         </is>
       </c>
     </row>
@@ -2138,37 +2138,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4068</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8430</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5200</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2744</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4519</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4068</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10403</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2445; 9142</t>
+          <t>2353; 9609</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>681; 7059</t>
+          <t>1414; 8421</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1768; 9993</t>
+          <t>719; 6393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>556; 5185</t>
+          <t>1965; 26005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2411; 9666</t>
+          <t>2013; 9589</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1426; 8346</t>
+          <t>677; 6954</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>720; 6362</t>
+          <t>1952; 9474</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2584; 24808</t>
+          <t>583; 5244</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6225; 15984</t>
+          <t>6074; 15742</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3401; 12192</t>
+          <t>3413; 11905</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3389; 12701</t>
+          <t>3383; 12945</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4173; 26536</t>
+          <t>4275; 26478</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>20035</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>14912</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>17473</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13968; 27982</t>
+          <t>11614; 25056</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9148; 21767</t>
+          <t>8733; 20159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8625; 21034</t>
+          <t>5763; 16416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4838; 14905</t>
+          <t>8342; 30526</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11336; 24622</t>
+          <t>14335; 27686</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8242; 20937</t>
+          <t>8974; 22241</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5292; 15409</t>
+          <t>8650; 20898</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9516; 32833</t>
+          <t>4428; 15038</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28707; 48048</t>
+          <t>28877; 48374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20538; 38228</t>
+          <t>20870; 37795</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16379; 31571</t>
+          <t>16009; 31894</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16252; 39753</t>
+          <t>16501; 40308</t>
         </is>
       </c>
     </row>
